--- a/pptx/testdata/golden/05-chart-bar/ppt/embeddings/Microsoft_Excel_Worksheet1.xlsx
+++ b/pptx/testdata/golden/05-chart-bar/ppt/embeddings/Microsoft_Excel_Worksheet1.xlsx
@@ -102,7 +102,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:B5'" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:B5" totalsRowShown="0">
   <tableColumns count="2">
     <tableColumn id="1" name="Column1"/>
     <tableColumn id="2" name="Revenue"/>
